--- a/papeles_trabajo/PT_Materialidad_2023_20251116.xlsx
+++ b/papeles_trabajo/PT_Materialidad_2023_20251116.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>557000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>650000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>520000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -599,148 +599,112 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Por Ingresos</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>3250</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Por Resultado</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Por Activo</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>5570</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1.0%</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AJUSTE POR RIESGO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Por Patrimonio</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+          <t>Evaluación de riesgo:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AUTO_ASSESSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Factor de ajuste:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>AJUSTE POR RIESGO</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>MATERIALIDAD DETERMINADA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Evaluación de riesgo:</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>AUTO_ASSESSED</t>
-        </is>
+          <t>Materialidad Global:</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Factor de ajuste:</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>MATERIALIDAD DETERMINADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Materialidad Global:</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>3250</v>
+          <t>Materialidad de Ejecución (75%):</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Umbral de Trivialidad (5%):</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Materialidad de Ejecución (75%):</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>2437.5</v>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>JUSTIFICACIÓN</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Umbral de Trivialidad (5%):</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>162.5</v>
-      </c>
+      <c r="A31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>JUSTIFICACIÓN DEL CÁLCULO DE MATERIALIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>JUSTIFICACIÓN</t>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>1. BASE DE CÁLCULO SELECCIONADA:</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr"/>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Se ha utilizado la base 'mixta' por ser la más apropiada para el tipo de entidad (mercantil).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>JUSTIFICACIÓN DEL CÁLCULO DE MATERIALIDAD</t>
+          <t xml:space="preserve">   Materialidad calculada: 0.00 €</t>
         </is>
       </c>
     </row>
@@ -750,110 +714,54 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>1. BASE DE CÁLCULO SELECCIONADA:</t>
+          <t>2. BASES CONSIDERADAS:</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Se ha utilizado la base 'por_ingresos' por ser la más apropiada para el tipo de entidad (mercantil).</t>
-        </is>
-      </c>
+      <c r="A39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Materialidad calculada: 3,250.00 €</t>
+          <t>4. CONCLUSIÓN:</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr"/>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   La materialidad global se establece en 0.00 €, cumpliendo con los parámetros de las NIA.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>2. BASES CONSIDERADAS:</t>
+          <t xml:space="preserve">   Esta cifra representa aproximadamente el 0.00% de los ingresos.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - por_ingresos: 3,250.00 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - por_resultado: 6,500.00 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - por_activo: 5,570.00 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - por_patrimonio: 3,000.00 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>4. CONCLUSIÓN:</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   La materialidad global se establece en 3,250.00 €, cumpliendo con los parámetros de las NIA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Esta cifra representa aproximadamente el 100.00% de los ingresos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr"/>
+      <c r="A43" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="15">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
